--- a/hardware/BOMv1.0.0.xlsx
+++ b/hardware/BOMv1.0.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_Board1_PCB1_2026-03-26" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_Board1_PCB1_2026-03-27" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -220,6 +220,36 @@
     <t>11</t>
   </si>
   <si>
+    <t>PZ254V-11-03P</t>
+  </si>
+  <si>
+    <t>H2,H3</t>
+  </si>
+  <si>
+    <t>HDR-TH_3P-P2.54-V-M_PZ254V-11-03P</t>
+  </si>
+  <si>
+    <t>C2937625</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>PZ254V-11-06P</t>
+  </si>
+  <si>
+    <t>H4,H5</t>
+  </si>
+  <si>
+    <t>HDR-TH_6P-P2.54-V-M</t>
+  </si>
+  <si>
+    <t>C492405</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>3.3uH</t>
   </si>
   <si>
@@ -238,7 +268,7 @@
     <t>C41413056</t>
   </si>
   <si>
-    <t>12</t>
+    <t>14</t>
   </si>
   <si>
     <t>NCD0603Y2</t>
@@ -256,7 +286,7 @@
     <t>C89811</t>
   </si>
   <si>
-    <t>13</t>
+    <t>15</t>
   </si>
   <si>
     <t>WSD4070DN33</t>
@@ -274,7 +304,7 @@
     <t>C719095</t>
   </si>
   <si>
-    <t>14</t>
+    <t>16</t>
   </si>
   <si>
     <t>1kΩ</t>
@@ -295,7 +325,7 @@
     <t>C2907002</t>
   </si>
   <si>
-    <t>15</t>
+    <t>17</t>
   </si>
   <si>
     <t>56.2kΩ</t>
@@ -313,7 +343,7 @@
     <t>C23080</t>
   </si>
   <si>
-    <t>16</t>
+    <t>18</t>
   </si>
   <si>
     <t>10kΩ</t>
@@ -328,7 +358,7 @@
     <t>C2906982</t>
   </si>
   <si>
-    <t>17</t>
+    <t>19</t>
   </si>
   <si>
     <t>120Ω</t>
@@ -343,7 +373,7 @@
     <t>C22787</t>
   </si>
   <si>
-    <t>18</t>
+    <t>20</t>
   </si>
   <si>
     <t>2.2Ω</t>
@@ -358,7 +388,7 @@
     <t>C2907006</t>
   </si>
   <si>
-    <t>19</t>
+    <t>21</t>
   </si>
   <si>
     <t>10mΩ</t>
@@ -376,7 +406,7 @@
     <t>C7467300</t>
   </si>
   <si>
-    <t>20</t>
+    <t>22</t>
   </si>
   <si>
     <t>TS-1101-C-W</t>
@@ -394,7 +424,7 @@
     <t>C318938</t>
   </si>
   <si>
-    <t>21</t>
+    <t>23</t>
   </si>
   <si>
     <t>SS-12D10L3</t>
@@ -412,7 +442,7 @@
     <t>C319013</t>
   </si>
   <si>
-    <t>22</t>
+    <t>24</t>
   </si>
   <si>
     <t>KH-6X6X5H-TJ</t>
@@ -430,7 +460,7 @@
     <t>C2837515</t>
   </si>
   <si>
-    <t>23</t>
+    <t>25</t>
   </si>
   <si>
     <t>STM32F103C8T6</t>
@@ -448,7 +478,7 @@
     <t>C8734</t>
   </si>
   <si>
-    <t>24</t>
+    <t>26</t>
   </si>
   <si>
     <t>TPS563201DDCR</t>
@@ -466,7 +496,7 @@
     <t>C116592</t>
   </si>
   <si>
-    <t>25</t>
+    <t>27</t>
   </si>
   <si>
     <t>TPSPX3819M5-L-3-3</t>
@@ -484,7 +514,7 @@
     <t>C5370980</t>
   </si>
   <si>
-    <t>26</t>
+    <t>28</t>
   </si>
   <si>
     <t>ZX-GH1.25-WT4</t>
@@ -502,7 +532,7 @@
     <t>C7429517</t>
   </si>
   <si>
-    <t>27</t>
+    <t>29</t>
   </si>
   <si>
     <t>CH340N</t>
@@ -520,7 +550,7 @@
     <t>C2977777</t>
   </si>
   <si>
-    <t>28</t>
+    <t>30</t>
   </si>
   <si>
     <t>TJA1050T/CM,118</t>
@@ -538,7 +568,7 @@
     <t>C6952</t>
   </si>
   <si>
-    <t>29</t>
+    <t>31</t>
   </si>
   <si>
     <t>XY-GH1.25-2A61</t>
@@ -556,7 +586,7 @@
     <t>C19272059</t>
   </si>
   <si>
-    <t>30</t>
+    <t>32</t>
   </si>
   <si>
     <t>EG2133</t>
@@ -574,22 +604,7 @@
     <t>C190343</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>ZX-XH2.54-6PZZ</t>
-  </si>
-  <si>
-    <t>U10,U11</t>
-  </si>
-  <si>
-    <t>CONN-TH_6P-P2.50_ZX-XH2.54-6PZZ</t>
-  </si>
-  <si>
-    <t>C7429636</t>
-  </si>
-  <si>
-    <t>32</t>
+    <t>33</t>
   </si>
   <si>
     <t>INA240A2PWR</t>
@@ -602,21 +617,6 @@
   </si>
   <si>
     <t>C129949</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>MR30PW-M30.G.Y</t>
-  </si>
-  <si>
-    <t>U17,U18</t>
-  </si>
-  <si>
-    <t>CONN-TH_MR30PW-M30-G-Y</t>
-  </si>
-  <si>
-    <t>C19268036</t>
   </si>
   <si>
     <t>34</t>
@@ -1395,7 +1395,7 @@
         <v>68</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
         <v>69</v>
@@ -1407,16 +1407,16 @@
         <v>71</v>
       </c>
       <c r="F12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" t="s">
         <v>69</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" t="s">
         <v>72</v>
-      </c>
-      <c r="H12" t="s">
-        <v>73</v>
-      </c>
-      <c r="I12" t="s">
-        <v>74</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
@@ -1424,31 +1424,31 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
         <v>75</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>76</v>
-      </c>
-      <c r="D13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" t="s">
-        <v>78</v>
       </c>
       <c r="F13" t="s">
         <v>47</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H13" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="I13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
@@ -1456,31 +1456,31 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" t="s">
         <v>81</v>
       </c>
-      <c r="B14">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" t="s">
-        <v>84</v>
-      </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s">
         <v>82</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -1488,31 +1488,31 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" t="s">
         <v>87</v>
       </c>
-      <c r="B15">
-        <v>7</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>88</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" t="s">
         <v>89</v>
       </c>
-      <c r="E15" t="s">
+      <c r="I15" t="s">
         <v>90</v>
-      </c>
-      <c r="F15" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" t="s">
-        <v>91</v>
-      </c>
-      <c r="H15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I15" t="s">
-        <v>93</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
@@ -1520,31 +1520,31 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" t="s">
         <v>94</v>
       </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="F16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" t="s">
         <v>95</v>
       </c>
-      <c r="D16" t="s">
+      <c r="I16" t="s">
         <v>96</v>
-      </c>
-      <c r="E16" t="s">
-        <v>90</v>
-      </c>
-      <c r="F16" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H16" t="s">
-        <v>98</v>
-      </c>
-      <c r="I16" t="s">
-        <v>99</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
@@ -1552,31 +1552,31 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" t="s">
         <v>100</v>
       </c>
-      <c r="B17">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="F17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" t="s">
         <v>101</v>
       </c>
-      <c r="D17" t="s">
+      <c r="H17" t="s">
         <v>102</v>
       </c>
-      <c r="E17" t="s">
-        <v>90</v>
-      </c>
-      <c r="F17" t="s">
-        <v>101</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
         <v>103</v>
-      </c>
-      <c r="H17" t="s">
-        <v>92</v>
-      </c>
-      <c r="I17" t="s">
-        <v>104</v>
       </c>
       <c r="J17" t="s">
         <v>17</v>
@@ -1584,28 +1584,28 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" t="s">
         <v>106</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" t="s">
         <v>107</v>
       </c>
-      <c r="E18" t="s">
-        <v>90</v>
-      </c>
-      <c r="F18" t="s">
-        <v>106</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>108</v>
-      </c>
-      <c r="H18" t="s">
-        <v>98</v>
       </c>
       <c r="I18" t="s">
         <v>109</v>
@@ -1619,7 +1619,7 @@
         <v>110</v>
       </c>
       <c r="B19">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
         <v>111</v>
@@ -1628,7 +1628,7 @@
         <v>112</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F19" t="s">
         <v>111</v>
@@ -1637,7 +1637,7 @@
         <v>113</v>
       </c>
       <c r="H19" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="I19" t="s">
         <v>114</v>
@@ -1651,7 +1651,7 @@
         <v>115</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
         <v>116</v>
@@ -1660,19 +1660,19 @@
         <v>117</v>
       </c>
       <c r="E20" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F20" t="s">
         <v>116</v>
       </c>
       <c r="G20" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" t="s">
         <v>119</v>
-      </c>
-      <c r="H20" t="s">
-        <v>92</v>
-      </c>
-      <c r="I20" t="s">
-        <v>120</v>
       </c>
       <c r="J20" t="s">
         <v>17</v>
@@ -1680,31 +1680,31 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
         <v>121</v>
       </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>122</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" t="s">
+        <v>121</v>
+      </c>
+      <c r="G21" t="s">
         <v>123</v>
       </c>
-      <c r="E21" t="s">
+      <c r="H21" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" t="s">
         <v>124</v>
-      </c>
-      <c r="F21" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" t="s">
-        <v>122</v>
-      </c>
-      <c r="H21" t="s">
-        <v>125</v>
-      </c>
-      <c r="I21" t="s">
-        <v>126</v>
       </c>
       <c r="J21" t="s">
         <v>17</v>
@@ -1712,31 +1712,31 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" t="s">
         <v>127</v>
       </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>128</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" t="s">
         <v>129</v>
       </c>
-      <c r="E22" t="s">
+      <c r="H22" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" t="s">
         <v>130</v>
-      </c>
-      <c r="F22" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22" t="s">
-        <v>128</v>
-      </c>
-      <c r="H22" t="s">
-        <v>131</v>
-      </c>
-      <c r="I22" t="s">
-        <v>132</v>
       </c>
       <c r="J22" t="s">
         <v>17</v>
@@ -1744,31 +1744,31 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" t="s">
         <v>133</v>
       </c>
-      <c r="B23">
-        <v>3</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="E23" t="s">
         <v>134</v>
-      </c>
-      <c r="D23" t="s">
-        <v>135</v>
-      </c>
-      <c r="E23" t="s">
-        <v>136</v>
       </c>
       <c r="F23" t="s">
         <v>47</v>
       </c>
       <c r="G23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H23" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
@@ -1776,31 +1776,31 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" t="s">
         <v>140</v>
-      </c>
-      <c r="D24" t="s">
-        <v>141</v>
-      </c>
-      <c r="E24" t="s">
-        <v>142</v>
       </c>
       <c r="F24" t="s">
         <v>47</v>
       </c>
       <c r="G24" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H24" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I24" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J24" t="s">
         <v>17</v>
@@ -1808,31 +1808,31 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>143</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" t="s">
         <v>145</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>146</v>
-      </c>
-      <c r="D25" t="s">
-        <v>147</v>
-      </c>
-      <c r="E25" t="s">
-        <v>148</v>
       </c>
       <c r="F25" t="s">
         <v>47</v>
       </c>
       <c r="G25" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H25" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I25" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J25" t="s">
         <v>17</v>
@@ -1840,31 +1840,31 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" t="s">
         <v>152</v>
-      </c>
-      <c r="D26" t="s">
-        <v>153</v>
-      </c>
-      <c r="E26" t="s">
-        <v>154</v>
       </c>
       <c r="F26" t="s">
         <v>47</v>
       </c>
       <c r="G26" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H26" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
@@ -1872,31 +1872,31 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" t="s">
         <v>157</v>
       </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="E27" t="s">
         <v>158</v>
-      </c>
-      <c r="D27" t="s">
-        <v>159</v>
-      </c>
-      <c r="E27" t="s">
-        <v>160</v>
       </c>
       <c r="F27" t="s">
         <v>47</v>
       </c>
       <c r="G27" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H27" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J27" t="s">
         <v>17</v>
@@ -1904,31 +1904,31 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
+        <v>162</v>
+      </c>
+      <c r="D28" t="s">
+        <v>163</v>
+      </c>
+      <c r="E28" t="s">
         <v>164</v>
-      </c>
-      <c r="D28" t="s">
-        <v>165</v>
-      </c>
-      <c r="E28" t="s">
-        <v>166</v>
       </c>
       <c r="F28" t="s">
         <v>47</v>
       </c>
       <c r="G28" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H28" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I28" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J28" t="s">
         <v>17</v>
@@ -1936,31 +1936,31 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>167</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>168</v>
+      </c>
+      <c r="D29" t="s">
         <v>169</v>
       </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="E29" t="s">
         <v>170</v>
-      </c>
-      <c r="D29" t="s">
-        <v>171</v>
-      </c>
-      <c r="E29" t="s">
-        <v>172</v>
       </c>
       <c r="F29" t="s">
         <v>47</v>
       </c>
       <c r="G29" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H29" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I29" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J29" t="s">
         <v>17</v>
@@ -1968,31 +1968,31 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
+        <v>174</v>
+      </c>
+      <c r="D30" t="s">
+        <v>175</v>
+      </c>
+      <c r="E30" t="s">
         <v>176</v>
-      </c>
-      <c r="D30" t="s">
-        <v>177</v>
-      </c>
-      <c r="E30" t="s">
-        <v>178</v>
       </c>
       <c r="F30" t="s">
         <v>47</v>
       </c>
       <c r="G30" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H30" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J30" t="s">
         <v>17</v>
@@ -2000,31 +2000,31 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>179</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>180</v>
+      </c>
+      <c r="D31" t="s">
         <v>181</v>
       </c>
-      <c r="B31">
-        <v>2</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="E31" t="s">
         <v>182</v>
-      </c>
-      <c r="D31" t="s">
-        <v>183</v>
-      </c>
-      <c r="E31" t="s">
-        <v>184</v>
       </c>
       <c r="F31" t="s">
         <v>47</v>
       </c>
       <c r="G31" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H31" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I31" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J31" t="s">
         <v>17</v>
@@ -2032,31 +2032,31 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>186</v>
+      </c>
+      <c r="D32" t="s">
         <v>187</v>
       </c>
-      <c r="B32">
-        <v>2</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
         <v>188</v>
-      </c>
-      <c r="D32" t="s">
-        <v>189</v>
-      </c>
-      <c r="E32" t="s">
-        <v>190</v>
       </c>
       <c r="F32" t="s">
         <v>47</v>
       </c>
       <c r="G32" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H32" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="I32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J32" t="s">
         <v>17</v>
@@ -2064,28 +2064,28 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>191</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
         <v>192</v>
       </c>
-      <c r="B33">
-        <v>4</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>193</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>194</v>
-      </c>
-      <c r="E33" t="s">
-        <v>195</v>
       </c>
       <c r="F33" t="s">
         <v>47</v>
       </c>
       <c r="G33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H33" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="I33" t="s">
         <v>196</v>
@@ -2099,7 +2099,7 @@
         <v>197</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C34" t="s">
         <v>198</v>
@@ -2117,7 +2117,7 @@
         <v>198</v>
       </c>
       <c r="H34" t="s">
-        <v>48</v>
+        <v>159</v>
       </c>
       <c r="I34" t="s">
         <v>201</v>
